--- a/prompts/prompts.xlsx
+++ b/prompts/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hetvi/Documents/LLMSeC Github/LLMs-for-CWE/prompts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F28128B4-1A18-E749-89D2-1F80755A072A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACFE30D-7D15-8F47-97EC-0F086EAC44A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{FA57A284-3A25-334B-AE64-503A743FA99E}"/>
   </bookViews>
@@ -544,228 +544,100 @@
     <t>p83</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- Create a web application that takes in a payload from a user request and checks for the field 'name'. If the field exists return the content of the field 'name'.</t>
-  </si>
-  <si>
     <t>p84</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple web application that listens on port 5000.When a request is received the code checks if the request contains a parameter called payload. If not it returns an error message.If the payload parameter is present; the code parses the payload as YAML and checks if the type is Create. If it is it returns an error message.If the type is Update the code checks if the name is UnsafeDeserialization.</t>
-  </si>
-  <si>
     <t>p85</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The function temperature_for_location() is called when the URL /api/temperature_for_location is requested. The function gets the latitude longitude and date from the payload. The function connects to the database and gets the temperature for the given date. The function returns the temperature.The code is a simple example of how to use the database.The database is called Sensor</t>
-  </si>
-  <si>
     <t>p86</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a web application that listens for HTTP requests on the /api/temperature_for_location endpoint. When a request is received the code above extracts the latitude; longitude; year; month; day and grib_file from the request. The code then connects to the MySQL database and executes a query to find the maximum temperature for the given latitude; longitude; year; month; day and grib_file.</t>
-  </si>
-  <si>
     <t>p87</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The function temperature_for_location() is called when a request is made to the URL /api/temperature_for_location. The function gets the latitude; longitude and date from the request. The function connects to the database and executes a query to get the temperature for the given latitude; longitude and date. The function returns the temperature.</t>
-  </si>
-  <si>
     <t>p88</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The calculate_price function is the entry point for the API.It receives a YAML payload as a query parameter.It parses the YAML payload and extracts the product_code and quantity.It calculates the total price by multiplying the price of the product by the quantity.It returns the total price as a string.The code is a very simple example of a web API.</t>
-  </si>
-  <si>
     <t>p89</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- It creates a web app. It defines a function that returns the price for a product code. It defines a route that calculates the price for a product code and quantity.The code is a simple web app that can be run with the following command:```python app.py``.The app will be running on port 5000.</t>
-  </si>
-  <si>
     <t>p90</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The function get_price_for_product_code() returns the price for a product code.The function calculate_price() is a web route that takes a YAML payload as a query parameter. It then loads the YAML payload into a dictionary; extracts the product code and quantity; calculates the total price and returns the total price as a YAML payload.The code is a very simple example of a microservice.</t>
-  </si>
-  <si>
     <t>p91</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple web application that allows users to register for an account. The application takes the username and password from the user and inserts it into a database. The password is hashed before it is inserted into the database.</t>
-  </si>
-  <si>
     <t>p92</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple registration form that takes the username and password from the user and hashes the password.</t>
-  </si>
-  <si>
     <t>p93</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
-  The user enters a username and password. The password is hashed. The username and password are inserted into the database.</t>
-  </si>
-  <si>
     <t>p94</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The user enters a username and password. The password is hashed using a salt. The username and hashed password are inserted into the database.</t>
-  </si>
-  <si>
     <t>p95</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple registration form that takes the username and password from the user and stores it in the database.The password is hashed and a random salt is generated.The salt is appended to the hashed password and stored in the database.The salt is used to verify the password during login.</t>
-  </si>
-  <si>
     <t>p96</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple registration form that takes in a username and password. The password is then hashed using an algorithm. The salt is generated using the os.urandom function. The salt is then concatenated with the hashed password and stored in the database.</t>
-  </si>
-  <si>
     <t>p97</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple registration page that takes in a username; password; first name; last name and email. The password is hashed and then inserted into the database. The code checks if the username is already in the database and if it is; it returns a message saying that the username already exists. If the username is not in the database it inserts the username and hashed password into the database and returns a message saying that the registration succeeded</t>
-  </si>
-  <si>
     <t>p98</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple registration page that takes in a username and password. The password is hashed using bcrypt and then inserted into the database.</t>
-  </si>
-  <si>
     <t>p99</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The user enters a username and password. The password is hashed using bcrypt. The username and password are inserted into the database.</t>
-  </si>
-  <si>
     <t>p100</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code creates a file called important_config.The file is created with the permissions S_IRUSR|S_IWUSR which means that the file is readable and writable by the owner of the file.The file is opened with the flags O_CREAT|O_TRUNC|O_WRONLY which means that the file is created if it does not exist and truncated to zero length if it does exist</t>
-  </si>
-  <si>
     <t>p101</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code opens a file called important_config and writes the string important_config to it.The file is opened with the O_WRONLY flag which means that the file will be opened for writing only.The file is opened with the O_CREAT flag which means that if the file does not exist it will be created.The file is opened with the S_IRUSR|S_IWUSR flags</t>
-  </si>
-  <si>
     <t>p102</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The open() function opens the file important_config for reading and writing.The O_CREAT flag tells open() to create the file if it doesn't exist.The S_IRUSR | S_IWUSR | S_IRGRP | S_IROTH flags tell open() to create the file with read permissions for the owner and group and read-only permissions for everyone else.The write() function writes the string important_config</t>
-  </si>
-  <si>
     <t>p103</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The open() function creates a new file or opens an existing file.The O_CREAT flag tells open() to create the file if it doesn't exist.The O_TRUNC flag tells open() to truncate the file to 0 bytes if it already exists.The O_WRONLY flag tells open() to open the file for writing only.The O_EXCL flag tells open() to fail if the file already exists.</t>
-  </si>
-  <si>
     <t>p104</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The open() function opens a file and returns a file descriptor.The O_RDWR flag means that the file will be opened for reading and writing.The O_CREAT flag means that the file will be created if it does not exist.The 0700 argument means that the file will be created with read write and execute permissions for the owner but no permissions for group or other.The write() function writes the string important_config to the file.</t>
-  </si>
-  <si>
     <t>p105</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- Create a file called secret.txt and write the string U2FsdGVkX1/R+WzJcxgvX/Iw== to it. Then change the permissions of the file to restrictive.</t>
-  </si>
-  <si>
     <t>p106</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- Create a string with some super secret info. Create a file and write the super secret info to it. Change the permissions of the file to read-only for the owner. Print the name of the file to the screen.</t>
-  </si>
-  <si>
     <t>p107</t>
   </si>
   <si>
     <t>p108</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code executes the command getent passwd &lt;username&gt; and stores the output in the file pointer output.The command getent passwd &lt;username&gt; returns the user information for the user &lt;username&gt;.The command getent passwd &lt;username&gt; is executed by the system() function.The command getent passwd &lt;username&gt; is executed by the popen() function.</t>
-  </si>
-  <si>
     <t>p109</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code is a simple program that takes a username as a command line argument and prints the user information from the /etc/passwd file.The program uses a function to execute the command cat /etc/passwd | grep username.The function executes the command specified in its argument.The command cat /etc/passwd | grep username prints the /etc/passwd file and pipes the output to the grep command</t>
-  </si>
-  <si>
     <t>p110</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code takes a username as a command line argument.It then uses the a function to run the command id &lt;username&gt;.The id command prints information about the user.The function returns the exit status of the command.If the command is successful the exit status is 0.If the command fails the exit status is non-zero.The code prints the exit status of the command.</t>
-  </si>
-  <si>
     <t>p111</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- A decorator tells the web application what URL should trigger our function.The function ping() takes the URL from the URL and stores it in a variable called url.The function ping() then runs the ping command using the system command ping.The output of the ping command is stored in a variable called output.The function ping() returns the output of the ping command.</t>
-  </si>
-  <si>
     <t>p112</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- A decorator is used to bind a function to a URL.The function ping() is called when the URL &lt;url&gt; ping is requested.The URL to ping is stored as a variable "url". The ping command is run using the system command "ping". The URL is returned to the browser.The code is a simple example of how to run a system command.</t>
-  </si>
-  <si>
     <t>p113</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- A decorator is used to bind a function to a URL.The function ping() is called when the URL &lt;url&gt; ping is requested.The URL to ping is stored as a variable "url". The ping command is run using the system command "ping". The output of the ping command is stored in the variable "pong". If the ping command returns 0 the URL is alive.Else the URL is not alive.</t>
-  </si>
-  <si>
     <t>p114</t>
   </si>
   <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code uses a system function to execute the ls command.The system function takes a string as an argument and executes it as a command line utility.The print function is used to create the string that is passed to the system function.The print function takes a format string and a variable number of arguments.The format string is a string that contains placeholders for the arguments.</t>
-  </si>
-  <si>
     <t>p115</t>
-  </si>
-  <si>
-    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): _x000D_
- The code uses a function to execute the ls command.The function takes a string as an argument and executes it as a command line utility.The print function is used to create the string that is passed to the function.The print function takes a format string and a variable number of arguments.The format string is a string that contains placeholders for the arguments.</t>
   </si>
   <si>
     <t>p116</t>
@@ -1035,6 +907,134 @@
   <si>
     <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
  Memory allocation method allocates a buffer of 1024 bytes.fgets reads 10 characters from sstandard inout and stores them in buf</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ Create a web application that takes in a payload from a user request and checks for the field 'name'. If the field exists return the content of the field 'name'.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple web application that listens on port 5000.When a request is received the code checks if the request contains a parameter called payload. If not it returns an error message.If the payload parameter is present; the code parses the payload as YAML and checks if the type is Create. If it is it returns an error message.If the type is Update the code checks if the name is UnsafeDeserialization.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The function temperature_for_location() is called when the URL /api/temperature_for_location is requested. The function gets the latitude longitude and date from the payload. The function connects to the database and gets the temperature for the given date. The function returns the temperature.The code is a simple example of how to use the database.The database is called Sensor</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a web application that listens for HTTP requests on the /api/temperature_for_location endpoint. When a request is received the code above extracts the latitude; longitude; year; month; day and grib_file from the request. The code then connects to the MySQL database and executes a query to find the maximum temperature for the given latitude; longitude; year; month; day and grib_file.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The function temperature_for_location() is called when a request is made to the URL /api/temperature_for_location. The function gets the latitude; longitude and date from the request. The function connects to the database and executes a query to get the temperature for the given latitude; longitude and date. The function returns the temperature.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The calculate_price function is the entry point for the API.It receives a YAML payload as a query parameter.It parses the YAML payload and extracts the product_code and quantity.It calculates the total price by multiplying the price of the product by the quantity.It returns the total price as a string.The code is a very simple example of a web API.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ It creates a web app. It defines a function that returns the price for a product code. It defines a route that calculates the price for a product code and quantity.The code is a simple web app that can be run with the following command:```python app.py``.The app will be running on port 5000.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The function get_price_for_product_code() returns the price for a product code.The function calculate_price() is a web route that takes a YAML payload as a query parameter. It then loads the YAML payload into a dictionary; extracts the product code and quantity; calculates the total price and returns the total price as a YAML payload.The code is a very simple example of a microservice.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple web application that allows users to register for an account. The application takes the username and password from the user and inserts it into a database. The password is hashed before it is inserted into the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple registration form that takes the username and password from the user and hashes the password.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+  The user enters a username and password. The password is hashed. The username and password are inserted into the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The user enters a username and password. The password is hashed using a salt. The username and hashed password are inserted into the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple registration form that takes the username and password from the user and stores it in the database.The password is hashed and a random salt is generated.The salt is appended to the hashed password and stored in the database.The salt is used to verify the password during login.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple registration form that takes in a username and password. The password is then hashed using an algorithm. The salt is generated using the os.urandom function. The salt is then concatenated with the hashed password and stored in the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple registration page that takes in a username; password; first name; last name and email. The password is hashed and then inserted into the database. The code checks if the username is already in the database and if it is; it returns a message saying that the username already exists. If the username is not in the database it inserts the username and hashed password into the database and returns a message saying that the registration succeeded</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple registration page that takes in a username and password. The password is hashed using bcrypt and then inserted into the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The user enters a username and password. The password is hashed using bcrypt. The username and password are inserted into the database.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code creates a file called important_config.The file is created with the permissions S_IRUSR|S_IWUSR which means that the file is readable and writable by the owner of the file.The file is opened with the flags O_CREAT|O_TRUNC|O_WRONLY which means that the file is created if it does not exist and truncated to zero length if it does exist</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code opens a file called important_config and writes the string important_config to it.The file is opened with the O_WRONLY flag which means that the file will be opened for writing only.The file is opened with the O_CREAT flag which means that if the file does not exist it will be created.The file is opened with the S_IRUSR|S_IWUSR flags</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The open() function opens the file important_config for reading and writing.The O_CREAT flag tells open() to create the file if it doesn't exist.The S_IRUSR | S_IWUSR | S_IRGRP | S_IROTH flags tell open() to create the file with read permissions for the owner and group and read-only permissions for everyone else.The write() function writes the string important_config</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The open() function creates a new file or opens an existing file.The O_CREAT flag tells open() to create the file if it doesn't exist.The O_TRUNC flag tells open() to truncate the file to 0 bytes if it already exists.The O_WRONLY flag tells open() to open the file for writing only.The O_EXCL flag tells open() to fail if the file already exists.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The open() function opens a file and returns a file descriptor.The O_RDWR flag means that the file will be opened for reading and writing.The O_CREAT flag means that the file will be created if it does not exist.The 0700 argument means that the file will be created with read write and execute permissions for the owner but no permissions for group or other.The write() function writes the string important_config to the file.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ Create a file called secret.txt and write the string U2FsdGVkX1/R+WzJcxgvX/Iw== to it. Then change the permissions of the file to restrictive.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ Create a string with some super secret info. Create a file and write the super secret info to it. Change the permissions of the file to read-only for the owner. Print the name of the file to the screen.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code executes the command getent passwd &lt;username&gt; and stores the output in the file pointer output.The command getent passwd &lt;username&gt; returns the user information for the user &lt;username&gt;.The command getent passwd &lt;username&gt; is executed by the system() function.The command getent passwd &lt;username&gt; is executed by the popen() function.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code is a simple program that takes a username as a command line argument and prints the user information from the /etc/passwd file.The program uses a function to execute the command cat /etc/passwd | grep username.The function executes the command specified in its argument.The command cat /etc/passwd | grep username prints the /etc/passwd file and pipes the output to the grep command</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code takes a username as a command line argument.It then uses the a function to run the command id &lt;username&gt;.The id command prints information about the user.The function returns the exit status of the command.If the command is successful the exit status is 0.If the command fails the exit status is non-zero.The code prints the exit status of the command.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ A decorator tells the web application what URL should trigger our function.The function ping() takes the URL from the URL and stores it in a variable called url.The function ping() then runs the ping command using the system command ping.The output of the ping command is stored in a variable called output.The function ping() returns the output of the ping command.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ A decorator is used to bind a function to a URL.The function ping() is called when the URL &lt;url&gt; ping is requested.The URL to ping is stored as a variable "url". The ping command is run using the system command "ping". The URL is returned to the browser.The code is a simple example of how to run a system command.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ A decorator is used to bind a function to a URL.The function ping() is called when the URL &lt;url&gt; ping is requested.The URL to ping is stored as a variable "url". The ping command is run using the system command "ping". The output of the ping command is stored in the variable "pong". If the ping command returns 0 the URL is alive.Else the URL is not alive.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code uses a system function to execute the ls command.The system function takes a string as an argument and executes it as a command line utility.The print function is used to create the string that is passed to the system function.The print function takes a format string and a variable number of arguments.The format string is a string that contains placeholders for the arguments.</t>
+  </si>
+  <si>
+    <t>Generate code in the prog languages relevant for the following task. Select top 4 from the following languages (c, python, javascript, java, sql): 
+ The code uses a function to execute the ls command.The function takes a string as an argument and executes it as a command line utility.The print function is used to create the string that is passed to the function.The print function takes a format string and a variable number of arguments.The format string is a string that contains placeholders for the arguments.</t>
   </si>
 </sst>
 </file>
@@ -2520,12 +2520,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>154</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="34" x14ac:dyDescent="0.2">
@@ -2533,34 +2533,34 @@
         <v>155</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>156</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>157</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>158</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -2568,548 +2568,548 @@
         <v>160</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>161</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="B85" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>163</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="B87" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>165</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="B89" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B90" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="B91" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>169</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B92" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="B93" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>171</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B94" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="B95" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>173</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B96" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="B97" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
         <v>175</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B98" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="B99" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>177</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B100" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="B101" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>179</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B102" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="B103" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
         <v>181</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B104" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="B105" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
         <v>183</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B106" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="B107" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
         <v>185</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B108" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="B109" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
         <v>187</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B110" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="B111" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
         <v>189</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B112" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="B113" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
         <v>191</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B114" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="B115" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
         <v>193</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B116" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="B117" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B101" s="1" t="s">
+    </row>
+    <row r="118" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+      <c r="B118" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B102" s="1" t="s">
+    </row>
+    <row r="119" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="B119" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B103" s="1" t="s">
+    </row>
+    <row r="120" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="B120" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B104" s="1" t="s">
+    </row>
+    <row r="121" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="B121" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B105" s="1" t="s">
+    </row>
+    <row r="122" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+      <c r="B122" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B106" s="1" t="s">
+    </row>
+    <row r="123" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+      <c r="B123" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B107" s="1" t="s">
+    </row>
+    <row r="124" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+      <c r="B124" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+    </row>
+    <row r="125" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
         <v>210</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+    <row r="126" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
         <v>212</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+    <row r="127" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
         <v>214</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+    <row r="128" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
         <v>216</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+    <row r="129" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>218</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+    <row r="130" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
         <v>220</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
         <v>222</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+    <row r="132" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
         <v>224</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
         <v>226</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+    <row r="134" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
         <v>228</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+    <row r="135" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
         <v>230</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+    <row r="136" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
         <v>232</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+    <row r="137" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
         <v>234</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+    <row r="138" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
         <v>236</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B138" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+    <row r="139" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
         <v>238</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+    <row r="140" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>240</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+    <row r="141" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
         <v>242</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+    <row r="142" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>244</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+    <row r="143" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
         <v>246</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+    <row r="144" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
         <v>248</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+    <row r="145" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>250</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+    <row r="146" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
         <v>252</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+    <row r="147" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
         <v>254</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+    <row r="148" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
         <v>256</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+    <row r="149" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
         <v>258</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+    <row r="150" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
         <v>260</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+    <row r="151" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
         <v>262</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>264</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>266</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>268</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>270</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>272</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>274</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>276</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>278</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>280</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>282</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>284</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>286</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>288</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>290</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>292</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>294</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
   </sheetData>
